--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/nov-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/nov-2025.xlsx
@@ -569,11 +569,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11436.138</v>
+        <v>484450.95</v>
       </c>
     </row>
     <row r="3">
@@ -630,11 +630,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>192.024</v>
+        <v>8134.41</v>
       </c>
     </row>
     <row r="4">
@@ -691,11 +691,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>289.632</v>
+        <v>12269.22</v>
       </c>
     </row>
     <row r="5">
@@ -752,11 +752,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>225.552</v>
+        <v>9554.700000000001</v>
       </c>
     </row>
     <row r="6">
@@ -813,11 +813,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>40.64</v>
+        <v>1721.57</v>
       </c>
     </row>
     <row r="7">
@@ -874,11 +874,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>165.608</v>
+        <v>7015.39</v>
       </c>
     </row>
     <row r="8">
@@ -935,11 +935,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>211.328</v>
+        <v>8952.15</v>
       </c>
     </row>
     <row r="9">
@@ -1000,11 +1000,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2633.472</v>
+        <v>111557.59</v>
       </c>
     </row>
     <row r="10">
@@ -1061,11 +1061,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>148.336</v>
+        <v>6283.72</v>
       </c>
     </row>
     <row r="11">
@@ -1122,11 +1122,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>756.92</v>
+        <v>32064.2</v>
       </c>
     </row>
     <row r="12">
@@ -1183,11 +1183,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>225.552</v>
+        <v>9554.700000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1244,11 +1244,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>225.552</v>
+        <v>9554.700000000001</v>
       </c>
     </row>
   </sheetData>
